--- a/data/23August-Towers-v-Tigers.xlsx
+++ b/data/23August-Towers-v-Tigers.xlsx
@@ -136,7 +136,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:O134"/>
   <sheetData>
     <row r="1">
@@ -377,8 +377,10 @@
       <c r="D22" t="s">
         <v>16</v>
       </c>
-      <c r="E22" t="s">
-        <v>21</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -418,8 +420,10 @@
       <c r="D26" t="s">
         <v>16</v>
       </c>
-      <c r="E26" t="s">
-        <v>23</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>DCLC</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -661,8 +665,10 @@
       <c r="D53" t="s">
         <v>16</v>
       </c>
-      <c r="E53" t="s">
-        <v>29</v>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>DCLCUC</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -702,8 +708,10 @@
       <c r="D57" t="s">
         <v>16</v>
       </c>
-      <c r="E57" t="s">
-        <v>30</v>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>DCUCLN</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -852,8 +860,10 @@
       <c r="D72" t="s">
         <v>16</v>
       </c>
-      <c r="E72" t="s">
-        <v>34</v>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>LCDCUC</t>
+        </is>
       </c>
     </row>
     <row r="73">
